--- a/assets/docs/lop3/Mi thuat - Lop 3.xlsx
+++ b/assets/docs/lop3/Mi thuat - Lop 3.xlsx
@@ -620,11 +620,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB1b: HS nhận ra nét riêng trong hoa văn của từng dân tộc qua ảnh phóng to.</t>
-        </is>
-      </c>
+      <c r="H6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -864,11 +860,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB1b: HS gọi tên được vật liệu qua ảnh chụp gần bề mặt.</t>
-        </is>
-      </c>
+      <c r="H14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
